--- a/project_code/target/classes/TestDataSheet.xlsx
+++ b/project_code/target/classes/TestDataSheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cognizantonline-my.sharepoint.com/personal/2110883_cognizant_com/Documents/Desktop/ninjaWeb_Automation/ninjaTutirial_CompleteProject/project_code/src/main/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="20" documentId="11_F25DC773A252ABDACC104896619C6DB05ADE5907" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3C20D733-F7EF-4C3F-8F46-9EABEDB3F513}"/>
+  <xr:revisionPtr revIDLastSave="44" documentId="11_F25DC773A252ABDACC104896619C6DB05ADE5907" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A5932A2A-9B7C-4D86-9D04-3648BF418ABC}"/>
   <bookViews>
     <workbookView xWindow="-109" yWindow="-109" windowWidth="26301" windowHeight="14169" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="24">
   <si>
     <t>First Name</t>
   </si>
@@ -58,6 +58,45 @@
   </si>
   <si>
     <t>New User</t>
+  </si>
+  <si>
+    <t>Pavan</t>
+  </si>
+  <si>
+    <t>Hiware</t>
+  </si>
+  <si>
+    <t>pavanhiware11@gmail.com</t>
+  </si>
+  <si>
+    <t>Valid User</t>
+  </si>
+  <si>
+    <t>Hiware12345</t>
+  </si>
+  <si>
+    <t>Invalid User</t>
+  </si>
+  <si>
+    <t>New Password</t>
+  </si>
+  <si>
+    <t>Hiware123</t>
+  </si>
+  <si>
+    <t>Used</t>
+  </si>
+  <si>
+    <t>Saicharn</t>
+  </si>
+  <si>
+    <t>Diware</t>
+  </si>
+  <si>
+    <t>saiDiware11@gamil.com</t>
+  </si>
+  <si>
+    <t>Sai@123</t>
   </si>
 </sst>
 </file>
@@ -123,11 +162,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -409,10 +449,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultColWidth="12.875" defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -429,10 +469,13 @@
         <v>5</v>
       </c>
       <c r="F1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -448,7 +491,71 @@
       <c r="E2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="2"/>
+      <c r="G2" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3">
+        <v>7218688193</v>
+      </c>
+      <c r="E3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4">
+        <v>7218688193</v>
+      </c>
+      <c r="E4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5">
+        <v>9881343521</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5" t="s">
         <v>10</v>
       </c>
     </row>
@@ -456,6 +563,10 @@
   <hyperlinks>
     <hyperlink ref="C2" r:id="rId1" xr:uid="{C9AA45D3-763C-49D8-8615-A269442DA2D2}"/>
     <hyperlink ref="E2" r:id="rId2" xr:uid="{D299E41E-0D4E-4B2E-B18E-81CE9669E643}"/>
+    <hyperlink ref="C3" r:id="rId3" xr:uid="{61631589-3655-490D-BACA-5AEC9D8923F7}"/>
+    <hyperlink ref="C4" r:id="rId4" xr:uid="{85C08829-7DF8-4628-9440-33B11E57217A}"/>
+    <hyperlink ref="C5" r:id="rId5" xr:uid="{F04DAC94-7373-4A61-903D-830C4109381B}"/>
+    <hyperlink ref="E5" r:id="rId6" xr:uid="{E7079178-30D0-4E88-913D-0A8DC63AD648}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
